--- a/output/laminas_comunales/comunal_m_movinterna_a_2022_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2022_magallanes.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala de colores estandarizada a nivel nacional para todo el periodo.</t>
+          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: Laguna Blanca (102,0); Torres del Paine (147,2); Primavera (112,6); San Gregorio (108,6); Río Verde (121,8); Cabo de Hornos ( 89,7); Timaukel (111,7).</t>
         </is>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_m_movinterna_a_2022_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_m_movinterna_a_2022_magallanes.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: Laguna Blanca (102,0); Torres del Paine (147,2); Primavera (112,6); San Gregorio (108,6); Río Verde (121,8); Cabo de Hornos ( 89,7); Timaukel (111,7).</t>
+          <t>Periodo 2018_2022. Escala comunal recortada a percentiles 3-97. Sobre umbral: Laguna Blanca (102,0); Torres del Paine (147,2); Primavera (112,6); San Gregorio (108,6); Río Verde (121,8); Cabo de Hornos ( 89,7); y 1 más.</t>
         </is>
       </c>
     </row>
